--- a/SGC-CKN/Excel/e5cd9f8b-2dbf-45a5-8c98-416f5437a459_Thi_công_cọc_khoan_nhồi_đại_trà_CT-02_D800_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/e5cd9f8b-2dbf-45a5-8c98-416f5437a459_Thi_công_cọc_khoan_nhồi_đại_trà_CT-02_D800_21-03-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>CT-02</t>
+    <t>P7-158</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/e5cd9f8b-2dbf-45a5-8c98-416f5437a459_Thi_công_cọc_khoan_nhồi_đại_trà_CT-02_D800_21-03-2026.xlsx
+++ b/SGC-CKN/Excel/e5cd9f8b-2dbf-45a5-8c98-416f5437a459_Thi_công_cọc_khoan_nhồi_đại_trà_CT-02_D800_21-03-2026.xlsx
@@ -233,7 +233,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -316,12 +316,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -332,7 +326,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,11 +406,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -512,7 +501,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -622,16 +611,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1500,16 +1486,16 @@
         <v>-39</v>
       </c>
       <c r="G19" s="31">
-        <v>-44.98</v>
+        <v>-41</v>
       </c>
       <c r="H19" s="31">
         <v>0.5</v>
       </c>
       <c r="I19" s="31">
-        <v>5.98</v>
-      </c>
-      <c r="J19" s="8">
-        <v>11.96</v>
+        <v>2</v>
+      </c>
+      <c r="J19" s="21">
+        <v>4</v>
       </c>
       <c r="K19" s="32" t="s">
         <v>30</v>
@@ -1532,38 +1518,38 @@
         <v>57</v>
       </c>
       <c r="F20" s="34">
+        <v>-41</v>
+      </c>
+      <c r="G20" s="34">
         <v>-44.98</v>
-      </c>
-      <c r="G20" s="34">
-        <v>-45</v>
       </c>
       <c r="H20" s="34">
         <v>0.33</v>
       </c>
       <c r="I20" s="34">
-        <v>0.02</v>
-      </c>
-      <c r="J20" s="37">
-        <v>0.06</v>
+        <v>3.98</v>
+      </c>
+      <c r="J20" s="8">
+        <v>11.94</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1934,16 +1920,16 @@
         <v>-39</v>
       </c>
       <c r="F10" s="31">
-        <v>-44.98</v>
+        <v>-41</v>
       </c>
       <c r="G10" s="31">
         <v>0.5</v>
       </c>
       <c r="H10" s="31">
-        <v>5.98</v>
-      </c>
-      <c r="I10" s="8">
-        <v>11.96</v>
+        <v>2</v>
+      </c>
+      <c r="I10" s="21">
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1960,47 +1946,47 @@
         <v>1</v>
       </c>
       <c r="E11" s="34">
+        <v>-41</v>
+      </c>
+      <c r="F11" s="34">
         <v>-44.98</v>
-      </c>
-      <c r="F11" s="34">
-        <v>-45</v>
       </c>
       <c r="G11" s="34">
         <v>0.33</v>
       </c>
       <c r="H11" s="34">
-        <v>0.02</v>
-      </c>
-      <c r="I11" s="37">
-        <v>0.06</v>
+        <v>3.98</v>
+      </c>
+      <c r="I11" s="8">
+        <v>11.94</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="40" t="s">
+      <c r="C12" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="39">
         <v>10</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="39">
         <v>0</v>
       </c>
-      <c r="F12" s="40">
-        <v>-45</v>
-      </c>
-      <c r="G12" s="40">
+      <c r="F12" s="39">
+        <v>-44.98</v>
+      </c>
+      <c r="G12" s="39">
         <v>6</v>
       </c>
-      <c r="H12" s="40">
-        <v>45</v>
-      </c>
-      <c r="I12" s="40">
+      <c r="H12" s="39">
+        <v>44.98</v>
+      </c>
+      <c r="I12" s="39">
         <v>7.5</v>
       </c>
     </row>
